--- a/data/trans_orig/IP22D1_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP22D1_2023-Estudios-trans_orig.xlsx
@@ -1108,7 +1108,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31873</t>
+          <t>32107</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>61364</t>
+          <t>61255</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4987</t>
+          <t>4753</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5707</t>
+          <t>5816</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48216</t>
+          <t>48424</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>96452</t>
+          <t>96686</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5056</t>
+          <t>4848</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4986</t>
+          <t>4752</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP22D1_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP22D1_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,64 +720,64 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5066</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>8192</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>3312</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>5658</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>13850</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5066</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5066</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5066</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>8192</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>8192</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>8192</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5658</t>
+          <t>3312</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5658</t>
+          <t>3312</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5658</t>
+          <t>3312</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>13850</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13850</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13850</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,34 +1068,34 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30211</t>
+          <t>32931</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>29568</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>34284</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>96,05%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>86,24%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
           <t>44</t>
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>35412</t>
+          <t>29862</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32107</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36860</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,27 +1138,27 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>65623</t>
+          <t>62793</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>61255</t>
+          <t>58343</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>67071</t>
+          <t>64146</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1176,107 +1176,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1353</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4716</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>3,95%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>13,76%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1448</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1353</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>4753</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>3,93%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>5803</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>2,11%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>12,9%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1448</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>5816</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>2,16%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>34284</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>34284</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>34284</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>30211</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>30211</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>30211</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>36860</t>
+          <t>29862</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>36860</t>
+          <t>29862</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36860</t>
+          <t>29862</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>67071</t>
+          <t>64146</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>67071</t>
+          <t>64146</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>67071</t>
+          <t>64146</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,64 +1406,64 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9150</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>9763</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>9856</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>10754</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>20517</t>
+          <t>19006</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9150</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9150</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>9150</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>9763</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>9763</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>9763</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10754</t>
+          <t>9856</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10754</t>
+          <t>9856</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10754</t>
+          <t>9856</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>20517</t>
+          <t>19006</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>20517</t>
+          <t>19006</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>20517</t>
+          <t>19006</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>47147</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>43052</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>97,21%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>88,77%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>48166</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>43031</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>51824</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>48424</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>53272</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>97,28%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,27 +1824,27 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>99990</t>
+          <t>90178</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>96686</t>
+          <t>86312</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>101438</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1862,107 +1862,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1353</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5448</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2,79%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>11,23%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1448</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1353</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>4848</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>2,72%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>5219</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>9,1%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1448</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>4752</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>48166</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>48166</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>48166</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>53272</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>53272</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>53272</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>101438</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>101438</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>101438</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
